--- a/www/download/COUNTRY.ESP.rpO2.xlsx
+++ b/www/download/COUNTRY.ESP.rpO2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>Espanha</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>0.748755221325691</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>0.760965480792957</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>0.878796386756267</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>0.896619689745689</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>0.938262371071927</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>1.082719769858</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>1.11656987802902</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>1.05752963938752</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.884017003011732</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>0.80392318278615</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>0.803793923544842</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>0.7964320001188</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>0.729660724615538</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.679902074660125</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.716948693257338</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13.569</t>
+          <t>-0.788824026751153</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13.796</t>
+          <t>-0.791802809164187</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>14.293</t>
+          <t>-0.752872538095471</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>14.932</t>
+          <t>-0.771276321392356</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>15.617</t>
+          <t>-0.835082225693143</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>16.412</t>
+          <t>-0.890172964365698</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>16.931</t>
+          <t>-0.895558015357179</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>17.338</t>
+          <t>-0.892546791090116</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>17.878</t>
+          <t>-0.894146738822439</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>18.51</t>
+          <t>-0.904566638061793</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>19.267</t>
+          <t>-0.918374031804041</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>20.022</t>
+          <t>-0.922096737084032</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>20.628</t>
+          <t>-0.904979572350836</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>20.576</t>
+          <t>-0.897402552435406</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>19.258</t>
+          <t>-0.845777809057137</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>11.022</t>
+          <t>-0.708854431502931</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>11.232</t>
+          <t>-0.714905483027807</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11.825</t>
+          <t>-0.661009660209215</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>-0.688681240577681</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>13.076</t>
+          <t>-0.776117166685786</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>13.815</t>
+          <t>-0.852017031559623</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>14.285</t>
+          <t>-0.858788704932842</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14.666</t>
+          <t>-0.854131465117994</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>15.204</t>
+          <t>-0.855750776269429</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>15.763</t>
+          <t>-0.874270302731423</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>16.458</t>
+          <t>-0.893986715795593</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>-0.900423375915434</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>17.759</t>
+          <t>-0.878135250070181</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>17.695</t>
+          <t>-0.870256622766249</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>16.561</t>
+          <t>-0.804396854763115</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>23514.494</t>
+          <t>-0.67648103311279</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>23846.269</t>
+          <t>-0.682731069162951</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>24704.464</t>
+          <t>-0.623005072373264</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>25856.859</t>
+          <t>-0.653609033079094</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>27049.908</t>
+          <t>-0.750766771998117</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>28401.149</t>
+          <t>-0.834959839336646</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>29231.75</t>
+          <t>-0.84244558665585</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>29836.085</t>
+          <t>-0.836784791263966</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>30494.884</t>
+          <t>-0.867327895060654</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>31273.815</t>
+          <t>-0.858886883277171</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>32133.3</t>
+          <t>-0.880727271174786</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>33146.634</t>
+          <t>-0.887923156070823</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>33757.146</t>
+          <t>-0.866069250819758</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>33692.434</t>
+          <t>-0.8561883730974</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>31673.494</t>
+          <t>-0.781831117543926</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>18384.955</t>
+          <t>529460446179.946</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>18810.323</t>
+          <t>539991755978.886</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>19852.46</t>
+          <t>460257085788.373</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>20871.514</t>
+          <t>490631441957.657</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>22043.548</t>
+          <t>723431228392.739</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>23299.203</t>
+          <t>1302565812348.08</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>24047.748</t>
+          <t>1390708621430.1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>24668.354</t>
+          <t>1360847319469.44</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>25346.447</t>
+          <t>1552220585292.73</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>26060.341</t>
+          <t>1818724882601.42</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>26899.087</t>
+          <t>2342620795759.27</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>27871.875</t>
+          <t>2646366142542.42</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>28470.212</t>
+          <t>2141118537551.22</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>28549.186</t>
+          <t>2126186581650.55</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>26760.757</t>
+          <t>1255203785054.51</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>27.34</t>
+          <t>173473606208.25</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>174704834875.22</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>147271810246.183</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>31.64</t>
+          <t>166520535837.811</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>32.55</t>
+          <t>239831899945.273</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>34.47</t>
+          <t>377842286786.557</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>410120024136.305</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>422602652906.075</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>496950482960.869</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>37.71</t>
+          <t>538296221246.154</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>38.94</t>
+          <t>652033795675.977</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>39.23</t>
+          <t>709369791512.432</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>598493909588.095</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>39.23</t>
+          <t>583967880446.463</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>40.64</t>
+          <t>384449627398.353</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16.18</t>
+          <t>22384885.5247694</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>22195476.7327419</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>20811234.6422738</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>18.63</t>
+          <t>20938954.2658971</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>31413288.6448756</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>54578498.7314876</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>57331874.6329589</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>51490204.1642495</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>46741685.8246405</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>21.19</t>
+          <t>45680994.2460716</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>22.67</t>
+          <t>52094328.423516</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>53110590.8736641</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>36853895.9054065</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>31651285.7695171</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>23039396.6589923</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>56.48</t>
+          <t>12970.8696079193</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>53.52</t>
+          <t>13098.6162571172</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>52.07</t>
+          <t>12687.5084516614</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>49.72</t>
+          <t>12785.1491128032</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>12121.1794646945</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>45.94</t>
+          <t>9513.29630307978</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>44.77</t>
+          <t>9336.2753804303</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>43.62</t>
+          <t>10380.8404201742</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>47.71</t>
+          <t>11378.5104296435</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>41.11</t>
+          <t>12648.2729977447</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>38.39</t>
+          <t>12476.1574701457</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>37.38</t>
+          <t>13513.1705625308</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>37.28</t>
+          <t>17474.6442192948</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>36.97</t>
+          <t>19478.3932864181</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>20609.4058544414</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>221970.003770939</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>235075.940198637</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>22.41</t>
+          <t>197370.7657054</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>23.96</t>
+          <t>206944.408329211</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>284144.045778814</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>26.66</t>
+          <t>403501.122299265</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>27.56</t>
+          <t>409770.796676972</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>28.22</t>
+          <t>421354.100403359</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>491376.069813715</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>29.78</t>
+          <t>621891.981406997</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>31.09</t>
+          <t>774331.899340464</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>31.67</t>
+          <t>927021.20488757</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>32.09</t>
+          <t>955871.320132572</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>1062113.92808241</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>33.63</t>
+          <t>724166.47783921</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16.02</t>
+          <t>-0.721763837117764</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>-0.729138574392902</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>-0.678949562905883</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>18.69</t>
+          <t>-0.705730453213997</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>19.26</t>
+          <t>-0.788982654046232</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>19.91</t>
+          <t>-0.860802945277815</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>19.97</t>
+          <t>-0.868032825929921</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>-0.864067141257275</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>20.77</t>
+          <t>-0.876095471263763</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>-0.88205230447677</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>-0.900427993532121</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>23.74</t>
+          <t>-0.905894969013121</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>-0.886211632175973</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>24.16</t>
+          <t>-0.878079404073111</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>-0.817230029112699</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>63.92</t>
+          <t>111897.430452834</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>61.07</t>
+          <t>117807.171481491</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>59.62</t>
+          <t>108524.751577177</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>111980.262251848</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>114414.474727125</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>53.42</t>
+          <t>111181.561355402</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>52.47</t>
+          <t>113379.834332325</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>51.55</t>
+          <t>126635.044450346</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>50.31</t>
+          <t>163392.96590868</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>48.69</t>
+          <t>193063.439321445</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>207955.822676289</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>226159.555082345</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>43.88</t>
+          <t>267551.938753399</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>43.37</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>42.49</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.748755221325691</t>
+          <t>15738.990077053</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.760965480792957</t>
+          <t>15554.7593286103</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.878796386756267</t>
+          <t>12454.1703872427</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.896619689745689</t>
+          <t>13418.686810035</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.938262371071927</t>
+          <t>18341.9380311006</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.082719769858</t>
+          <t>27350.7413687273</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11656987802902</t>
+          <t>28710.4401307906</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05752963938752</t>
+          <t>28814.7340760439</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884017003011732</t>
+          <t>32686.1542230424</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.80392318278615</t>
+          <t>34149.784381338</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793923544842</t>
+          <t>39618.0456723768</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.7964320001188</t>
+          <t>41289.9612060647</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660724615538</t>
+          <t>33701.0687366951</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679902074660125</t>
+          <t>33002.604209559</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716948693257338</t>
+          <t>23213.4545420616</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>260381475122.725</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.305</t>
+          <t>277193735025.624</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>233800886776.715</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>246318847602.192</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>319889864745.765</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>525777482429.42</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>595506564007.555</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>622209871078.005</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.428</t>
+          <t>704453402495.806</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.499</t>
+          <t>729958296663.487</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.536</t>
+          <t>844935202448.296</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.583</t>
+          <t>879854240306.985</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.688</t>
+          <t>708254574090.251</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>781701153714.293</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.727</t>
+          <t>594674318561.872</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>276197973679</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>292088885122.003</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>245777564562.125</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>260137098983.704</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>339285477406.504</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>562641188678.267</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>638236362344.281</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.393</t>
+          <t>660382241184.185</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.498</t>
+          <t>753251172350.003</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.579</t>
+          <t>792141512418.474</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>903872670354.706</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.673</t>
+          <t>951451301060.087</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.793</t>
+          <t>775374280547.534</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.902</t>
+          <t>839359639018.011</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.836</t>
+          <t>629200797386.141</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.112</t>
+          <t>-15816498556.2757</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.181</t>
+          <t>-14895150096.3796</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.986</t>
+          <t>-11976677785.41</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2.035</t>
+          <t>-13818251381.512</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2.095</t>
+          <t>-19395612660.7394</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.023</t>
+          <t>-36863706248.8467</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.119</t>
+          <t>-42729798336.7254</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2.449</t>
+          <t>-38172370106.1794</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>3.214</t>
+          <t>-48797769854.1965</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>3.893</t>
+          <t>-62183215754.9868</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>4.255</t>
+          <t>-58937467906.41</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>4.685</t>
+          <t>-71597060753.1021</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>5.504</t>
+          <t>-67119706457.2831</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-57658485303.7176</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-34526478824.2685</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.137</t>
+          <t>4379.15620668081</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.181</t>
+          <t>4213.1842867227</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.085</t>
+          <t>3998.41684646887</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.131</t>
+          <t>3948.71088605233</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.158</t>
+          <t>3870.46708297134</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.104</t>
+          <t>3807.14264299506</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.159</t>
+          <t>3788.83565036863</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>3916.86917686806</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.695</t>
+          <t>4049.96253520604</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>4027.88837039401</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2.201</t>
+          <t>3944.84829993463</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2.435</t>
+          <t>3885.59307874374</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2.839</t>
+          <t>3834.78960547388</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>3.192</t>
+          <t>4023.6971723687</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2.909</t>
+          <t>4242.72241084628</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>4364.91794580444</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>4185.43231110884</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.525</t>
+          <t>3985.96625731616</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.548</t>
+          <t>3946.8952705546</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>3872.10886161182</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.527</t>
+          <t>3767.19707081799</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.554</t>
+          <t>3753.60911866168</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.626</t>
+          <t>3872.30563774416</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>4006.69872374719</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.941</t>
+          <t>3980.2898316501</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1.012</t>
+          <t>3897.93033745129</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1.101</t>
+          <t>3847.57369050005</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.295</t>
+          <t>3802.66205714456</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>3899.07381728167</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>3904.85324440528</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-78.88</t>
+          <t>109520.280260737</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-79.18</t>
+          <t>121019.906945021</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-75.29</t>
+          <t>125440.923317723</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-77.13</t>
+          <t>132596.03965942</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-83.51</t>
+          <t>134697.557195567</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-89.02</t>
+          <t>140903.507170301</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-89.56</t>
+          <t>144886.601118099</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-89.25</t>
+          <t>158476.850079172</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-89.41</t>
+          <t>195988.313768716</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-90.46</t>
+          <t>229314.211284507</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-91.84</t>
+          <t>245985.920616821</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-92.21</t>
+          <t>278285.203619124</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-90.5</t>
+          <t>334952.87473209</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-89.74</t>
+          <t>366573.171549866</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-84.58</t>
+          <t>293688.174509799</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-70.89</t>
+          <t>86531213101.2628</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-71.49</t>
+          <t>91200020289.3703</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-66.1</t>
+          <t>87820570351.2585</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-68.87</t>
+          <t>99493521236.2229</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-77.61</t>
+          <t>146477078961.804</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-85.2</t>
+          <t>280647343254.496</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-85.88</t>
+          <t>289686919111.614</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-85.41</t>
+          <t>270034004392.525</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-85.58</t>
+          <t>316278355521.502</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-87.43</t>
+          <t>383595637641.468</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-89.4</t>
+          <t>477994732490.122</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-90.04</t>
+          <t>594727776325.312</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-87.81</t>
+          <t>512752736639.491</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-87.03</t>
+          <t>541982290233.549</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-80.44</t>
+          <t>274728984488.143</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-67.65</t>
+          <t>124770.118251857</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-68.27</t>
+          <t>133889.711107774</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-62.3</t>
+          <t>135377.567732083</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-65.36</t>
+          <t>150396.284162831</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-75.08</t>
+          <t>164268.961420969</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-83.5</t>
+          <t>175674.697712927</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-84.24</t>
+          <t>177717.690062476</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-83.68</t>
+          <t>190692.877611322</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-86.73</t>
+          <t>238769.467007788</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-85.89</t>
+          <t>293693.971671943</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-88.07</t>
+          <t>326928.67876476</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-88.79</t>
+          <t>377946.471463735</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-86.61</t>
+          <t>453611.854891462</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-85.62</t>
+          <t>483950.566419665</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-78.18</t>
+          <t>350325.246453118</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>59228.885</t>
+          <t>410056507104.143</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>57742.22</t>
+          <t>419496922764.887</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>56972.615</t>
+          <t>355747273582.568</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>58935.04</t>
+          <t>412646336685.783</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>60471.107</t>
+          <t>612104209267.497</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>61825.355</t>
+          <t>1050800461075.1</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>63550.855</t>
+          <t>1132494711207.3</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>67136.486</t>
+          <t>1124739419607.32</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>71630.157</t>
+          <t>1317050932045.18</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>73674.369</t>
+          <t>1522416990484.89</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>75102.593</t>
+          <t>1862544853118.51</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>77036.12</t>
+          <t>2092347582648.29</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>78443.214</t>
+          <t>1768452675396.98</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>80228.58</t>
+          <t>1796970961707.06</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>75198.593</t>
+          <t>1053015580141.01</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>48266.631</t>
+          <t>-15249.8379911202</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>47320.801</t>
+          <t>-12869.8041627527</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>47281.679</t>
+          <t>-9936.64441436082</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>49001.923</t>
+          <t>-17800.2445034108</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>50608.691</t>
+          <t>-29571.4042254017</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>52594.533</t>
+          <t>-34771.1905426264</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>54122.381</t>
+          <t>-32831.0889443763</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>57445.587</t>
+          <t>-32216.0275321508</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>61574.415</t>
+          <t>-42781.1532390726</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>63490.799</t>
+          <t>-64379.7603874361</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>64924.313</t>
+          <t>-80942.7581479387</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>66755.266</t>
+          <t>-99661.2678446112</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>68101.645</t>
+          <t>-118658.980159372</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>71197.712</t>
+          <t>-117377.394869799</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>70265.847</t>
+          <t>-56637.0719433188</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>529460.446</t>
+          <t>-323525294002.88</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>539991.756</t>
+          <t>-328296902475.517</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>460257.086</t>
+          <t>-267926703231.31</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>490631.442</t>
+          <t>-313152815449.56</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>723431.228</t>
+          <t>-465627130305.692</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1302565.812</t>
+          <t>-770153117820.602</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1390708.621</t>
+          <t>-842807792095.683</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1360847.319</t>
+          <t>-854705415214.793</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1552220.585</t>
+          <t>-1000772576523.68</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1818724.883</t>
+          <t>-1138821352843.42</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2342620.796</t>
+          <t>-1384550120628.39</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2646366.143</t>
+          <t>-1497619806322.98</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2141118.538</t>
+          <t>-1255699938757.49</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2126186.582</t>
+          <t>-1254988671473.51</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1255203.785</t>
+          <t>-778286595652.868</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>266375.37769</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>278035.05396</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>252297.51342</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>260955.44354</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t>263350.98525</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>246557.79417</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>257872.79854</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.421</t>
+          <t>288378.67913</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.491</t>
+          <t>369600.35736</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.622</t>
+          <t>433637.20248</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>466138.1344</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.927</t>
+          <t>503621.1502</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.956</t>
+          <t>585940.81553</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1.062</t>
+          <t>654300.10674</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.724</t>
+          <t>591298.93665</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>30939.146</t>
+          <t>0.0382210135319761</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>30088.765</t>
+          <t>0.0379299984927473</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>29586.528</t>
+          <t>0.0371796406325024</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>30311.503</t>
+          <t>0.0383553601013954</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>30860.544</t>
+          <t>0.0377885410089678</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>30710.434</t>
+          <t>0.0379940731320384</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>31686.101</t>
+          <t>0.0416998527072626</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>33527</t>
+          <t>0.0433946513048132</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>35943.871</t>
+          <t>0.0429779092718767</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>36989.911</t>
+          <t>0.0434680078153492</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>37744.675</t>
+          <t>0.0433471913371612</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>38576.029</t>
+          <t>0.0430494340166089</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>39142.596</t>
+          <t>0.0426223933143097</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>38992.708</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>35722.455</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>291808.316733849</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>305132.106559137</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>284654.105695089</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>297978.063926283</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>306337.553877687</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>288325.761286174</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>299763.592259955</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>335934.791999997</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>428228.190224466</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>498930.754307214</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>535998.080271348</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>583286.457455248</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>688240.415189618</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>783200.673539864</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>727079.091269295</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>173473.606</t>
+          <t>358083.445359631</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>174704.835</t>
+          <t>372331.088725999</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>147271.81</t>
+          <t>342997.313917794</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>166520.536</t>
+          <t>358380.819232282</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>239831.9</t>
+          <t>366035.373843655</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>377842.287</t>
+          <t>338929.567248008</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>410120.024</t>
+          <t>351984.377498107</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>422602.653</t>
+          <t>392605.991558936</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>496950.483</t>
+          <t>498162.302385956</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>538296.221</t>
+          <t>578956.463825489</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>652033.796</t>
+          <t>620027.285849691</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>709369.792</t>
+          <t>673117.318416295</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>598493.91</t>
+          <t>792753.100788172</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>583967.88</t>
+          <t>902445.44325516</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>384449.627</t>
+          <t>835809.727677538</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-72.18</t>
+          <t>2112166.5018118</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-72.91</t>
+          <t>2180500.62823819</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-67.89</t>
+          <t>1985902.06707059</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-70.57</t>
+          <t>2034912.54597896</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-78.9</t>
+          <t>2095213.63527716</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-86.08</t>
+          <t>2022897.09422545</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-86.8</t>
+          <t>2118527.5765778</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-86.41</t>
+          <t>2449366.85224449</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-87.61</t>
+          <t>3213887.97397246</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-88.21</t>
+          <t>3892532.23570367</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-90.04</t>
+          <t>4254845.27958112</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-90.59</t>
+          <t>4684517.58514539</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-88.62</t>
+          <t>5503591.05807592</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-87.81</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-81.72</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>22.385</t>
+          <t>358083.445359631</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>22.195</t>
+          <t>365829.935846962</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>20.811</t>
+          <t>381569.691012317</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>20.939</t>
+          <t>397102.440614817</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>31.413</t>
+          <t>414710.268884059</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>54.578</t>
+          <t>427270.86837679</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>57.332</t>
+          <t>437485.250962429</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>51.49</t>
+          <t>442468.031891349</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>46.742</t>
+          <t>451075.692171595</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>45.681</t>
+          <t>459626.088998396</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>52.094</t>
+          <t>473503.168458034</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>53.111</t>
+          <t>492135.084105528</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>36.854</t>
+          <t>511999.508728918</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>31.651</t>
+          <t>520129.075526616</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>23.039</t>
+          <t>497819.439729837</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>291808.316733849</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>299450.510346145</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>316084.751467274</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>329625.822547258</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>346500.191208835</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>363089.5603355</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>372924.047543774</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>378930.134595833</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>388669.644566182</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>396925.803602501</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>410391.417042076</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>426629.233357581</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>444414.086390273</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>450928.707152788</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>431377.285263621</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>192626.574900369</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>200513.557024001</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>182359.876762206</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>190030.065727718</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>193589.541106345</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>188039.661491992</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>201722.122231893</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>232924.464921064</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>301519.151664044</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>362264.060964511</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>392391.415120309</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>427825.385763705</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>502128.161471828</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>562487.57750484</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>530674.386332462</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>48266630552.7277</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>47320800634.7547</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>47281679051.179</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>49001922611.555</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>50608691001.5012</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>52594533470.1839</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>54122380614.8208</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>57445586721.7824</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>61574415396.5121</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>63490798804.8467</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>64924313320.3242</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>66755266211.4332</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>68101645124.6501</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>71197711986.1952</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>70265847207.2307</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>59228885446.6921</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>57742219979.4287</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>56972615492.3239</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>58935040179.7129</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>60471107430.2988</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>61825354727.7294</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>63550854544.4135</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>67136486224.9531</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>71630157103.6628</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>73674368725.8771</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>75102593190.7753</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>77036120431.192</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>78443214245.8065</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>80228579574.1286</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>75198593114.0936</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>30939146250.7601</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>30088765305.3629</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>29586527898.4285</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>30311503439.5103</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>30860543727.6651</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>30710433855.8409</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>31686100544.2646</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>33526999846.7101</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>35943871107.8391</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>36989910644.7542</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>37744675074.8931</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>38576029185.2435</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>39142595752.1722</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>38992708166.8782</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>35722454750.1952</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>13569300.9999473</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>13795999.000192</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>14293301.0001657</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>14931999.9999472</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>15617098.9999302</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>16411500</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>16930600</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>17337600</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>17877600</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>18509800</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>19267300</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>20022000</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>20628500</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>20576317.1803866</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>19257725.8112927</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>11021902</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>11231600</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>11825100</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>12409600</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>13075603</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>13814700</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>14284700</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>14666200</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>15203700</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>15762800</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>16458000</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>17180200</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>17758900</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>17694600</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>16561500</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>23514493699.9123</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>23846269000.3119</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>24704463700.2885</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>25856858599.9331</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>27049908499.8955</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>28401148900</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>29231750000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>29836085000</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>30494883600</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>31273815100</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>32133300400</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>33146633700</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>33757145700</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>33692434300.156</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>31673493566.3532</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>18384954800</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>18810322900</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>19852460200</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>20871513900</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>22043548100</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>23299203000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>24047748300</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>24668354200</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>25346447300</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>26060341300</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>26899086800</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>27871875300</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>28470211500</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>28549185900</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>26760757000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.27337934115787</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.293012019827709</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.299484675333469</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.316421547069308</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.325520561365048</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.344668661286352</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.356745111723183</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.366531484113573</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.33902574594464</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.377072787961434</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.389438216927018</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.392341691075884</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.393971012044968</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.392324552249411</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.406426619648174</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.161798090887162</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.171762080787493</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.179831615394149</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.186337128429743</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.190972227950267</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.195922528300967</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.195522472732045</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.19724866341156</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.183891902154676</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.211860667773598</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.226658017483415</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.233821687109926</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.233229578689497</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.237976856018813</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.234416934733873</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.564822567954968</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.535225899384799</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.520683709272383</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.497241324500948</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.483507210684685</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.459408810412681</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.447732415544772</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.436219852474868</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.477082351900684</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.411066544264968</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.383903765589567</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.37383662181419</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.372799409265536</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.369698591731777</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.359156445617952</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.200670069665548</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.218043292182423</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.224069172303285</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.239637678914906</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.247476783015023</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.266639805201482</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.275602465726367</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.282187873220182</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.289157307595638</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.297779523753416</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.310856327494752</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.316681289933401</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.3208652051446</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.32467331842563</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.336291443854847</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.160151761310241</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.1713049132251</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.179745371785676</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.186945277395556</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.192565543844875</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.199111439255819</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.199713364057565</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.20228078575005</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.207694714792361</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.215276170376725</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.231039037491323</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.237354213442524</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.240328230587112</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.241598508970236</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.238850083680788</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.639178169024211</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.610651794592476</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.596185455911039</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.573417043689538</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.559957673140102</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.534248755542699</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.524684170216068</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.515531341029768</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.503147977612</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.48694430586986</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.458104635013924</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.445964496624076</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.438806564268288</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.433728172604134</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.424858472464365</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1137233.09765</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1180804.65846</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1084757.01577</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1131351.21011</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1157813.60464</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1103652.15177</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1159249.44985</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1325268.7549</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1695348.59695</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2010355.01228</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2200858.88681</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2435198.48464</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2838946.82881</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>3191602.43002</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2909046.49266</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>550710.02026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>572844.64575</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>525357.19068</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>548410.88496</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>559624.91495</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>526969.22874</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>553706.49973</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>625530.45648</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>799681.45405</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>941220.52479</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>1012418.70097</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>1100942.70418</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1294881.26226</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>1464933.02076</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1366484.11401</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1581495.68696843</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1628629.82506667</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1680335.50608497</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1742909.88908419</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1816023.17662004</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1895094.92228355</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1977427.19883719</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2059411.54591606</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2146976.35014075</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2239591.37491869</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2341608.52453285</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>2454893.7597595</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>2578693.7714082</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO2</t>
